--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M631"/>
+  <dimension ref="A1:M633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28843,6 +28843,96 @@
         <v>349.81</v>
       </c>
       <c r="M631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>330.06</v>
+      </c>
+      <c r="C632" t="n">
+        <v>341.79</v>
+      </c>
+      <c r="D632" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="E632" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="F632" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="G632" t="n">
+        <v>346.51</v>
+      </c>
+      <c r="H632" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="I632" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="J632" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="K632" t="n">
+        <v>354.82</v>
+      </c>
+      <c r="L632" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="C633" t="n">
+        <v>340.51</v>
+      </c>
+      <c r="D633" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="E633" t="n">
+        <v>347.18</v>
+      </c>
+      <c r="F633" t="n">
+        <v>343.16</v>
+      </c>
+      <c r="G633" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="H633" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="I633" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="J633" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="K633" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="L633" t="n">
+        <v>354.54</v>
+      </c>
+      <c r="M633" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28859,7 +28949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35522,6 +35612,26 @@
       </c>
       <c r="B666" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -35690,28 +35800,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2540360122246244</v>
+        <v>-0.2546808267422065</v>
       </c>
       <c r="J2" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K2" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08094589817702891</v>
+        <v>0.08182461202807201</v>
       </c>
       <c r="M2" t="n">
-        <v>4.844103008805416</v>
+        <v>4.83139372683757</v>
       </c>
       <c r="N2" t="n">
-        <v>36.90954858485373</v>
+        <v>36.79591384995455</v>
       </c>
       <c r="O2" t="n">
-        <v>6.075322920212039</v>
+        <v>6.065963554947767</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5869918310508</v>
+        <v>337.5941327232808</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35772,28 +35882,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.24150364145612</v>
+        <v>-0.2423545296153845</v>
       </c>
       <c r="J3" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K3" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1186356421365288</v>
+        <v>0.1200542750879398</v>
       </c>
       <c r="M3" t="n">
-        <v>3.783953774220653</v>
+        <v>3.776235515029625</v>
       </c>
       <c r="N3" t="n">
-        <v>21.82677615279057</v>
+        <v>21.7643618188763</v>
       </c>
       <c r="O3" t="n">
-        <v>4.671913542949031</v>
+        <v>4.665229021053125</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8158239438794</v>
+        <v>348.8252484117315</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35850,28 +35960,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2088034998860409</v>
+        <v>-0.2082262472584579</v>
       </c>
       <c r="J4" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K4" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08622598030516904</v>
+        <v>0.08631105926574267</v>
       </c>
       <c r="M4" t="n">
-        <v>3.793200779122763</v>
+        <v>3.783955015917414</v>
       </c>
       <c r="N4" t="n">
-        <v>23.27438114959183</v>
+        <v>23.20428895610405</v>
       </c>
       <c r="O4" t="n">
-        <v>4.824352925480455</v>
+        <v>4.817083033964025</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0773150538955</v>
+        <v>353.0709247734684</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35928,28 +36038,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1758506215224882</v>
+        <v>-0.1752559620169218</v>
       </c>
       <c r="J5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06772504244716249</v>
+        <v>0.06771229893175901</v>
       </c>
       <c r="M5" t="n">
-        <v>3.676633932355565</v>
+        <v>3.667683011769166</v>
       </c>
       <c r="N5" t="n">
-        <v>21.44294722839195</v>
+        <v>21.37929585224459</v>
       </c>
       <c r="O5" t="n">
-        <v>4.630653002373634</v>
+        <v>4.623775065057186</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5942217871454</v>
+        <v>351.5876391549529</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36006,28 +36116,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06944795429776948</v>
+        <v>-0.07143722655348927</v>
       </c>
       <c r="J6" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008429707371164996</v>
+        <v>0.008965903380478202</v>
       </c>
       <c r="M6" t="n">
-        <v>4.103622050551997</v>
+        <v>4.10007838056718</v>
       </c>
       <c r="N6" t="n">
-        <v>28.57800131225491</v>
+        <v>28.51734645942348</v>
       </c>
       <c r="O6" t="n">
-        <v>5.345839626499743</v>
+        <v>5.340163523659503</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3773593621191</v>
+        <v>348.3993887418936</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36084,28 +36194,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002075419073513403</v>
+        <v>0.001662036726237581</v>
       </c>
       <c r="J7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L7" t="n">
-        <v>5.588556583502324e-06</v>
+        <v>3.608215184081054e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.923785374139749</v>
+        <v>4.910341703675381</v>
       </c>
       <c r="N7" t="n">
-        <v>38.82499931382143</v>
+        <v>38.70371335663962</v>
       </c>
       <c r="O7" t="n">
-        <v>6.230970976807822</v>
+        <v>6.221230855436858</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7838381027688</v>
+        <v>346.7884167517295</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36162,28 +36272,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2314935913143997</v>
+        <v>0.229807622018845</v>
       </c>
       <c r="J8" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K8" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0752933104843645</v>
+        <v>0.07470419651943327</v>
       </c>
       <c r="M8" t="n">
-        <v>4.618099326947717</v>
+        <v>4.61294325122574</v>
       </c>
       <c r="N8" t="n">
-        <v>33.15335475281444</v>
+        <v>33.06966915735121</v>
       </c>
       <c r="O8" t="n">
-        <v>5.757894993208406</v>
+        <v>5.750623371196484</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5021011205612</v>
+        <v>346.5207712937141</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36240,28 +36350,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2998151046121724</v>
+        <v>0.295471803753651</v>
       </c>
       <c r="J9" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K9" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09094358682069192</v>
+        <v>0.08885539308942758</v>
       </c>
       <c r="M9" t="n">
-        <v>5.306099494216521</v>
+        <v>5.312083937942121</v>
       </c>
       <c r="N9" t="n">
-        <v>45.26137075517429</v>
+        <v>45.25858817779817</v>
       </c>
       <c r="O9" t="n">
-        <v>6.7276571520236</v>
+        <v>6.727450347479212</v>
       </c>
       <c r="P9" t="n">
-        <v>350.5030008120769</v>
+        <v>350.5510961481283</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36318,28 +36428,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3335432637468957</v>
+        <v>0.3271479298916938</v>
       </c>
       <c r="J10" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K10" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09630188867789113</v>
+        <v>0.09306669757829478</v>
       </c>
       <c r="M10" t="n">
-        <v>5.856675788931639</v>
+        <v>5.872228185209544</v>
       </c>
       <c r="N10" t="n">
-        <v>52.58899206082955</v>
+        <v>52.72721075900662</v>
       </c>
       <c r="O10" t="n">
-        <v>7.251826808524149</v>
+        <v>7.26135047763201</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5364493874477</v>
+        <v>356.6072675194338</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36396,28 +36506,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1481071988336939</v>
+        <v>0.1419263090175648</v>
       </c>
       <c r="J11" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K11" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02489180467676633</v>
+        <v>0.02290788570170987</v>
       </c>
       <c r="M11" t="n">
-        <v>5.245745731762236</v>
+        <v>5.259227108666587</v>
       </c>
       <c r="N11" t="n">
-        <v>43.28632215184359</v>
+        <v>43.43518911547215</v>
       </c>
       <c r="O11" t="n">
-        <v>6.579234161499619</v>
+        <v>6.590537847207324</v>
       </c>
       <c r="P11" t="n">
-        <v>359.7507366266353</v>
+        <v>359.819183314827</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -36478,28 +36588,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4729330842150361</v>
+        <v>-0.4713516959401056</v>
       </c>
       <c r="J12" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K12" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1400860488729279</v>
+        <v>0.1400599796472312</v>
       </c>
       <c r="M12" t="n">
-        <v>6.675499165455355</v>
+        <v>6.663097280104743</v>
       </c>
       <c r="N12" t="n">
-        <v>69.16102646853302</v>
+        <v>68.96196837135065</v>
       </c>
       <c r="O12" t="n">
-        <v>8.316310868920969</v>
+        <v>8.304334312354642</v>
       </c>
       <c r="P12" t="n">
-        <v>365.1653802839312</v>
+        <v>365.1478707587507</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -36541,7 +36651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M631"/>
+  <dimension ref="A1:M633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78821,6 +78931,140 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-45.562721288628126,170.73163552108176</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-45.563302020813865,170.73125200747447</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-45.563856113120536,170.73082559252686</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-45.564402422348905,170.73040059508236</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-45.56494568491974,170.72995023588345</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-45.56552083151789,170.72958639953802</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-45.56610525284528,170.72925678462138</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-45.566688135635964,170.7289254135622</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-45.56727716628156,170.72863089351705</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>-45.56787356534468,170.72835913705018</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>-45.56845763464889,170.72805721754565</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-45.562719674329365,170.73163228290468</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-45.563295355294585,170.73123863683077</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-45.5638504812142,170.7308129307651</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-45.56439640539281,170.73038469442832</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-45.56494300734661,170.7299428335776</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-45.565518350634655,170.7295792861692</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-45.56610408290999,170.72925317980122</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-45.566689002727266,170.72892822920147</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>-45.567278870375645,170.72863723453725</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>-45.56786923452277,170.7283422961076</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>-45.56845353347497,170.72804258273575</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M633"/>
+  <dimension ref="A1:M634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28935,6 +28935,51 @@
       <c r="M633" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="C634" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="D634" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="E634" t="n">
+        <v>346.72</v>
+      </c>
+      <c r="F634" t="n">
+        <v>343.42</v>
+      </c>
+      <c r="G634" t="n">
+        <v>345</v>
+      </c>
+      <c r="H634" t="n">
+        <v>348.98</v>
+      </c>
+      <c r="I634" t="n">
+        <v>351.09</v>
+      </c>
+      <c r="J634" t="n">
+        <v>356.66</v>
+      </c>
+      <c r="K634" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="L634" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B668"/>
+  <dimension ref="A1:B669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35632,6 +35677,16 @@
       </c>
       <c r="B668" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -35800,28 +35855,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2546808267422065</v>
+        <v>-0.2546541632410827</v>
       </c>
       <c r="J2" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K2" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08182461202807201</v>
+        <v>0.0820635199784191</v>
       </c>
       <c r="M2" t="n">
-        <v>4.83139372683757</v>
+        <v>4.823912003667322</v>
       </c>
       <c r="N2" t="n">
-        <v>36.79591384995455</v>
+        <v>36.73779506200412</v>
       </c>
       <c r="O2" t="n">
-        <v>6.065963554947767</v>
+        <v>6.061171096578954</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5941327232808</v>
+        <v>337.5938368144924</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35882,28 +35937,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2423545296153845</v>
+        <v>-0.2432993587318935</v>
       </c>
       <c r="J3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1200542750879398</v>
+        <v>0.1211736897564639</v>
       </c>
       <c r="M3" t="n">
-        <v>3.776235515029625</v>
+        <v>3.774967146793154</v>
       </c>
       <c r="N3" t="n">
-        <v>21.7643618188763</v>
+        <v>21.74331131113825</v>
       </c>
       <c r="O3" t="n">
-        <v>4.665229021053125</v>
+        <v>4.662972368686979</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8252484117315</v>
+        <v>348.8357340279268</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35960,28 +36015,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2082262472584579</v>
+        <v>-0.2082263656482121</v>
       </c>
       <c r="J4" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K4" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08631105926574267</v>
+        <v>0.08657850272240752</v>
       </c>
       <c r="M4" t="n">
-        <v>3.783955015917414</v>
+        <v>3.777977789320782</v>
       </c>
       <c r="N4" t="n">
-        <v>23.20428895610405</v>
+        <v>23.16763131183297</v>
       </c>
       <c r="O4" t="n">
-        <v>4.817083033964025</v>
+        <v>4.813276567145603</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0709247734684</v>
+        <v>353.0709260873457</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36038,28 +36093,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1752559620169218</v>
+        <v>-0.1753370964745304</v>
       </c>
       <c r="J5" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K5" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06771229893175901</v>
+        <v>0.06798466340185694</v>
       </c>
       <c r="M5" t="n">
-        <v>3.667683011769166</v>
+        <v>3.662311752453402</v>
       </c>
       <c r="N5" t="n">
-        <v>21.37929585224459</v>
+        <v>21.34561960636254</v>
       </c>
       <c r="O5" t="n">
-        <v>4.623775065057186</v>
+        <v>4.620131990145145</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5876391549529</v>
+        <v>351.5885395768046</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36116,28 +36171,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07143722655348927</v>
+        <v>-0.07244068048395357</v>
       </c>
       <c r="J6" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K6" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008965903380478202</v>
+        <v>0.009243347416325154</v>
       </c>
       <c r="M6" t="n">
-        <v>4.10007838056718</v>
+        <v>4.098356738632583</v>
       </c>
       <c r="N6" t="n">
-        <v>28.51734645942348</v>
+        <v>28.48733355405633</v>
       </c>
       <c r="O6" t="n">
-        <v>5.340163523659503</v>
+        <v>5.337352672819769</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3993887418936</v>
+        <v>348.4105249702345</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36194,28 +36249,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001662036726237581</v>
+        <v>0.001069079581445504</v>
       </c>
       <c r="J7" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K7" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L7" t="n">
-        <v>3.608215184081054e-06</v>
+        <v>1.497764189117845e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.910341703675381</v>
+        <v>4.905632759275652</v>
       </c>
       <c r="N7" t="n">
-        <v>38.70371335663962</v>
+        <v>38.64782111521004</v>
       </c>
       <c r="O7" t="n">
-        <v>6.221230855436858</v>
+        <v>6.216737175979859</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7884167517295</v>
+        <v>346.7949973290338</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36272,28 +36327,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.229807622018845</v>
+        <v>0.2286410255057174</v>
       </c>
       <c r="J8" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K8" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07470419651943327</v>
+        <v>0.07419369531639497</v>
       </c>
       <c r="M8" t="n">
-        <v>4.61294325122574</v>
+        <v>4.612158183614726</v>
       </c>
       <c r="N8" t="n">
-        <v>33.06966915735121</v>
+        <v>33.03775193815784</v>
       </c>
       <c r="O8" t="n">
-        <v>5.750623371196484</v>
+        <v>5.747847591764924</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5207712937141</v>
+        <v>346.5337180616298</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36350,28 +36405,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.295471803753651</v>
+        <v>0.2931201720405526</v>
       </c>
       <c r="J9" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K9" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08885539308942758</v>
+        <v>0.08769467414999776</v>
       </c>
       <c r="M9" t="n">
-        <v>5.312083937942121</v>
+        <v>5.316161613284875</v>
       </c>
       <c r="N9" t="n">
-        <v>45.25858817779817</v>
+        <v>45.26968189698641</v>
       </c>
       <c r="O9" t="n">
-        <v>6.727450347479212</v>
+        <v>6.728274808372976</v>
       </c>
       <c r="P9" t="n">
-        <v>350.5510961481283</v>
+        <v>350.5771943146067</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36428,28 +36483,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3271479298916938</v>
+        <v>0.32436611850896</v>
       </c>
       <c r="J10" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K10" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09306669757829478</v>
+        <v>0.09173441678804573</v>
       </c>
       <c r="M10" t="n">
-        <v>5.872228185209544</v>
+        <v>5.877783398376975</v>
       </c>
       <c r="N10" t="n">
-        <v>52.72721075900662</v>
+        <v>52.75948637571864</v>
       </c>
       <c r="O10" t="n">
-        <v>7.26135047763201</v>
+        <v>7.263572562845273</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6072675194338</v>
+        <v>356.6381397755672</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36506,28 +36561,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1419263090175648</v>
+        <v>0.1384623885699427</v>
       </c>
       <c r="J11" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K11" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02290788570170987</v>
+        <v>0.02181168251917842</v>
       </c>
       <c r="M11" t="n">
-        <v>5.259227108666587</v>
+        <v>5.267818692328233</v>
       </c>
       <c r="N11" t="n">
-        <v>43.43518911547215</v>
+        <v>43.54577056427561</v>
       </c>
       <c r="O11" t="n">
-        <v>6.590537847207324</v>
+        <v>6.598921924396106</v>
       </c>
       <c r="P11" t="n">
-        <v>359.819183314827</v>
+        <v>359.8576255470892</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -36588,28 +36643,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4713516959401056</v>
+        <v>-0.4711431977735035</v>
       </c>
       <c r="J12" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K12" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1400599796472312</v>
+        <v>0.1403602866296544</v>
       </c>
       <c r="M12" t="n">
-        <v>6.663097280104743</v>
+        <v>6.653719003852141</v>
       </c>
       <c r="N12" t="n">
-        <v>68.96196837135065</v>
+        <v>68.85367295364122</v>
       </c>
       <c r="O12" t="n">
-        <v>8.304334312354642</v>
+        <v>8.297811335143818</v>
       </c>
       <c r="P12" t="n">
-        <v>365.1478707587507</v>
+        <v>365.145556867578</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -36651,7 +36706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M633"/>
+  <dimension ref="A1:M634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79065,6 +79120,73 @@
         </is>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-45.56272597530144,170.7316449222421</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-45.563290199930954,170.73122829547572</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-45.56384898899947,170.73080957593976</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-45.564394442413764,170.73037950698165</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-45.564944078375916,170.72994579449986</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-45.56551478936605,170.72956907504414</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-45.566100837282505,170.72924317933317</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-45.56668636532434,170.72891966496564</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>-45.56728189273035,170.72864848087593</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>-45.56786756406221,170.7283358003162</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>-45.568449599013704,170.72802854283887</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M634"/>
+  <dimension ref="A1:M636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28980,6 +28980,96 @@
       <c r="M634" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>333.67</v>
+      </c>
+      <c r="C635" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="D635" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="E635" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="F635" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="G635" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="H635" t="n">
+        <v>350.13</v>
+      </c>
+      <c r="I635" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="J635" t="n">
+        <v>356.88</v>
+      </c>
+      <c r="K635" t="n">
+        <v>351.92</v>
+      </c>
+      <c r="L635" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>330.49</v>
+      </c>
+      <c r="C636" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="D636" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="E636" t="n">
+        <v>345.99</v>
+      </c>
+      <c r="F636" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="G636" t="n">
+        <v>348.06</v>
+      </c>
+      <c r="H636" t="n">
+        <v>350.75</v>
+      </c>
+      <c r="I636" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="J636" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="K636" t="n">
+        <v>354.49</v>
+      </c>
+      <c r="L636" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28994,7 +29084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B669"/>
+  <dimension ref="A1:B671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35687,6 +35777,26 @@
       </c>
       <c r="B669" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -35855,28 +35965,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2546541632410827</v>
+        <v>-0.2538401896879904</v>
       </c>
       <c r="J2" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K2" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0820635199784191</v>
+        <v>0.0820783473618496</v>
       </c>
       <c r="M2" t="n">
-        <v>4.823912003667322</v>
+        <v>4.814346416105637</v>
       </c>
       <c r="N2" t="n">
-        <v>36.73779506200412</v>
+        <v>36.63484091428273</v>
       </c>
       <c r="O2" t="n">
-        <v>6.061171096578954</v>
+        <v>6.052672212691079</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5938368144924</v>
+        <v>337.5847377493527</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35937,28 +36047,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2432993587318935</v>
+        <v>-0.2450531250331607</v>
       </c>
       <c r="J3" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K3" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1211736897564639</v>
+        <v>0.1233481977708731</v>
       </c>
       <c r="M3" t="n">
-        <v>3.774967146793154</v>
+        <v>3.771641252872409</v>
       </c>
       <c r="N3" t="n">
-        <v>21.74331131113825</v>
+        <v>21.69758226319188</v>
       </c>
       <c r="O3" t="n">
-        <v>4.662972368686979</v>
+        <v>4.658066365262723</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8357340279268</v>
+        <v>348.855347488239</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36015,28 +36125,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2082263656482121</v>
+        <v>-0.2079197472391814</v>
       </c>
       <c r="J4" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K4" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08657850272240752</v>
+        <v>0.08688790437372684</v>
       </c>
       <c r="M4" t="n">
-        <v>3.777977789320782</v>
+        <v>3.768232960192186</v>
       </c>
       <c r="N4" t="n">
-        <v>23.16763131183297</v>
+        <v>23.09685148205008</v>
       </c>
       <c r="O4" t="n">
-        <v>4.813276567145603</v>
+        <v>4.8059183807104</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0709260873457</v>
+        <v>353.0674987973216</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36093,28 +36203,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1753370964745304</v>
+        <v>-0.1760398649611118</v>
       </c>
       <c r="J5" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K5" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06798466340185694</v>
+        <v>0.06892693365361846</v>
       </c>
       <c r="M5" t="n">
-        <v>3.662311752453402</v>
+        <v>3.654367083058355</v>
       </c>
       <c r="N5" t="n">
-        <v>21.34561960636254</v>
+        <v>21.28204662898212</v>
       </c>
       <c r="O5" t="n">
-        <v>4.620131990145145</v>
+        <v>4.613246864084137</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5885395768046</v>
+        <v>351.5963990618412</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36171,28 +36281,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07244068048395357</v>
+        <v>-0.07297282284265012</v>
       </c>
       <c r="J6" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K6" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009243347416325154</v>
+        <v>0.009442344952420134</v>
       </c>
       <c r="M6" t="n">
-        <v>4.098356738632583</v>
+        <v>4.08791824848696</v>
       </c>
       <c r="N6" t="n">
-        <v>28.48733355405633</v>
+        <v>28.40002492240025</v>
       </c>
       <c r="O6" t="n">
-        <v>5.337352672819769</v>
+        <v>5.329167376091714</v>
       </c>
       <c r="P6" t="n">
-        <v>348.4105249702345</v>
+        <v>348.4164774829001</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36249,28 +36359,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001069079581445504</v>
+        <v>0.001061612707339076</v>
       </c>
       <c r="J7" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K7" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L7" t="n">
-        <v>1.497764189117845e-06</v>
+        <v>1.487022542989713e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.905632759275652</v>
+        <v>4.894123693073843</v>
       </c>
       <c r="N7" t="n">
-        <v>38.64782111521004</v>
+        <v>38.53102392937427</v>
       </c>
       <c r="O7" t="n">
-        <v>6.216737175979859</v>
+        <v>6.207336299039571</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7949973290338</v>
+        <v>346.7950772630583</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36327,28 +36437,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2286410255057174</v>
+        <v>0.2272246320085411</v>
       </c>
       <c r="J8" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K8" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07419369531639497</v>
+        <v>0.07378716243252303</v>
       </c>
       <c r="M8" t="n">
-        <v>4.612158183614726</v>
+        <v>4.605364384960405</v>
       </c>
       <c r="N8" t="n">
-        <v>33.03775193815784</v>
+        <v>32.94862806643933</v>
       </c>
       <c r="O8" t="n">
-        <v>5.747847591764924</v>
+        <v>5.740089552127155</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5337180616298</v>
+        <v>346.549558327918</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36405,28 +36515,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2931201720405526</v>
+        <v>0.2896343957319113</v>
       </c>
       <c r="J9" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K9" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08769467414999776</v>
+        <v>0.08618856808928455</v>
       </c>
       <c r="M9" t="n">
-        <v>5.316161613284875</v>
+        <v>5.31757013279276</v>
       </c>
       <c r="N9" t="n">
-        <v>45.26968189698641</v>
+        <v>45.21720605225161</v>
       </c>
       <c r="O9" t="n">
-        <v>6.728274808372976</v>
+        <v>6.72437402679622</v>
       </c>
       <c r="P9" t="n">
-        <v>350.5771943146067</v>
+        <v>350.6161777738062</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36483,28 +36593,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.32436611850896</v>
+        <v>0.3196829757192217</v>
       </c>
       <c r="J10" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K10" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09173441678804573</v>
+        <v>0.08965119289107393</v>
       </c>
       <c r="M10" t="n">
-        <v>5.877783398376975</v>
+        <v>5.883906196746559</v>
       </c>
       <c r="N10" t="n">
-        <v>52.75948637571864</v>
+        <v>52.75787623651114</v>
       </c>
       <c r="O10" t="n">
-        <v>7.263572562845273</v>
+        <v>7.263461725411041</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6381397755672</v>
+        <v>356.6905132654932</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36561,28 +36671,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1384623885699427</v>
+        <v>0.1317095343471669</v>
       </c>
       <c r="J11" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K11" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02181168251917842</v>
+        <v>0.01976152083634741</v>
       </c>
       <c r="M11" t="n">
-        <v>5.267818692328233</v>
+        <v>5.283457171997163</v>
       </c>
       <c r="N11" t="n">
-        <v>43.54577056427561</v>
+        <v>43.74640228951562</v>
       </c>
       <c r="O11" t="n">
-        <v>6.598921924396106</v>
+        <v>6.614106310720717</v>
       </c>
       <c r="P11" t="n">
-        <v>359.8576255470892</v>
+        <v>359.9331467657605</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -36643,28 +36753,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4711431977735035</v>
+        <v>-0.4798549374958391</v>
       </c>
       <c r="J12" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K12" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1403602866296544</v>
+        <v>0.1446959130618385</v>
       </c>
       <c r="M12" t="n">
-        <v>6.653719003852141</v>
+        <v>6.669194263887988</v>
       </c>
       <c r="N12" t="n">
-        <v>68.85367295364122</v>
+        <v>69.19596175631376</v>
       </c>
       <c r="O12" t="n">
-        <v>8.297811335143818</v>
+        <v>8.318411011504166</v>
       </c>
       <c r="P12" t="n">
-        <v>365.145556867578</v>
+        <v>365.2429941200907</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -36706,7 +36816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M634"/>
+  <dimension ref="A1:M636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79187,6 +79297,140 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-45.562740087391,170.73167323019</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-45.56328947088956,170.73122683306204</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-45.56385438022642,170.7308216965999</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-45.56439021774067,170.7303683426955</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-45.564954747471454,170.72997528984686</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-45.56551703016438,170.72957550002155</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-45.56610517736557,170.72925655205236</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-45.56669088142486,170.72893432975346</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>-45.56728260008979,170.72865111299794</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>-45.5678645943537,170.7283242522435</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>-45.568407320119846,170.72787767356607</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-45.56272352781658,170.73164001274708</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-45.56329275157569,170.73123341392395</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-45.56384773746447,170.73080676221545</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-45.564391327250874,170.73037127473006</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-45.5649519875131,170.72996765977533</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-45.565527033724074,170.72960418296285</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-45.56610751723582,170.72926376169312</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-45.56669586719769,170.72895051968203</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>-45.56729038103987,170.72868006634437</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>-45.5678725445083,170.72835516739917</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>-45.568398184118706,170.72784507250776</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M636"/>
+  <dimension ref="A1:M642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29065,9 +29065,279 @@
         <v>354.49</v>
       </c>
       <c r="L636" t="n">
-        <v>337.94</v>
+        <v>341.41</v>
       </c>
       <c r="M636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="C637" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="D637" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="E637" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="F637" t="n">
+        <v>344.52</v>
+      </c>
+      <c r="G637" t="n">
+        <v>345.3</v>
+      </c>
+      <c r="H637" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="I637" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="J637" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="K637" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="L637" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="C638" t="n">
+        <v>339.78</v>
+      </c>
+      <c r="D638" t="n">
+        <v>348.82</v>
+      </c>
+      <c r="E638" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="F638" t="n">
+        <v>346.64</v>
+      </c>
+      <c r="G638" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="H638" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="I638" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="J638" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="K638" t="n">
+        <v>356.38</v>
+      </c>
+      <c r="L638" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="C639" t="n">
+        <v>340.86</v>
+      </c>
+      <c r="D639" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="E639" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="F639" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="G639" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="H639" t="n">
+        <v>352.05</v>
+      </c>
+      <c r="I639" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="J639" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="K639" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="L639" t="n">
+        <v>345.52</v>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>329.43</v>
+      </c>
+      <c r="C640" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="D640" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="E640" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="F640" t="n">
+        <v>347.49</v>
+      </c>
+      <c r="G640" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="H640" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="I640" t="n">
+        <v>358.86</v>
+      </c>
+      <c r="J640" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="K640" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="L640" t="n">
+        <v>345.52</v>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="C641" t="n">
+        <v>341.84</v>
+      </c>
+      <c r="D641" t="n">
+        <v>350.13</v>
+      </c>
+      <c r="E641" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="F641" t="n">
+        <v>348.51</v>
+      </c>
+      <c r="G641" t="n">
+        <v>345.78</v>
+      </c>
+      <c r="H641" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="I641" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="J641" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="K641" t="n">
+        <v>365.08</v>
+      </c>
+      <c r="L641" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>332.31</v>
+      </c>
+      <c r="C642" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="D642" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="E642" t="n">
+        <v>352.51</v>
+      </c>
+      <c r="F642" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="G642" t="n">
+        <v>346.47</v>
+      </c>
+      <c r="H642" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="I642" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="J642" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="K642" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="L642" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="M642" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29084,7 +29354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B671"/>
+  <dimension ref="A1:B677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35797,6 +36067,66 @@
       </c>
       <c r="B671" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -35965,28 +36295,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2538401896879904</v>
+        <v>-0.2544960264215813</v>
       </c>
       <c r="J2" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K2" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0820783473618496</v>
+        <v>0.08403612222297896</v>
       </c>
       <c r="M2" t="n">
-        <v>4.814346416105637</v>
+        <v>4.777278234177593</v>
       </c>
       <c r="N2" t="n">
-        <v>36.63484091428273</v>
+        <v>36.30200331902355</v>
       </c>
       <c r="O2" t="n">
-        <v>6.052672212691079</v>
+        <v>6.025114382235706</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5847377493527</v>
+        <v>337.5920984914384</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36047,28 +36377,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2450531250331607</v>
+        <v>-0.2478965357620275</v>
       </c>
       <c r="J3" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K3" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1233481977708731</v>
+        <v>0.1279827696905318</v>
       </c>
       <c r="M3" t="n">
-        <v>3.771641252872409</v>
+        <v>3.752644471884639</v>
       </c>
       <c r="N3" t="n">
-        <v>21.69758226319188</v>
+        <v>21.53132293306938</v>
       </c>
       <c r="O3" t="n">
-        <v>4.658066365262723</v>
+        <v>4.640185657176809</v>
       </c>
       <c r="P3" t="n">
-        <v>348.855347488239</v>
+        <v>348.8872964823606</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36125,28 +36455,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2079197472391814</v>
+        <v>-0.2044100686682523</v>
       </c>
       <c r="J4" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K4" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08688790437372684</v>
+        <v>0.08570883813508223</v>
       </c>
       <c r="M4" t="n">
-        <v>3.768232960192186</v>
+        <v>3.749318894847312</v>
       </c>
       <c r="N4" t="n">
-        <v>23.09685148205008</v>
+        <v>22.92026947862799</v>
       </c>
       <c r="O4" t="n">
-        <v>4.8059183807104</v>
+        <v>4.787511825429572</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0674987973216</v>
+        <v>353.0280120117633</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36203,28 +36533,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1760398649611118</v>
+        <v>-0.1720802519957282</v>
       </c>
       <c r="J5" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06892693365361846</v>
+        <v>0.06712179491509185</v>
       </c>
       <c r="M5" t="n">
-        <v>3.654367083058355</v>
+        <v>3.640905132957771</v>
       </c>
       <c r="N5" t="n">
-        <v>21.28204662898212</v>
+        <v>21.16311975027817</v>
       </c>
       <c r="O5" t="n">
-        <v>4.613246864084137</v>
+        <v>4.600339090793001</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5963990618412</v>
+        <v>351.5518308040016</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36281,28 +36611,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07297282284265012</v>
+        <v>-0.0707287620200174</v>
       </c>
       <c r="J6" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K6" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009442344952420134</v>
+        <v>0.009047756101805415</v>
       </c>
       <c r="M6" t="n">
-        <v>4.08791824848696</v>
+        <v>4.066754717422142</v>
       </c>
       <c r="N6" t="n">
-        <v>28.40002492240025</v>
+        <v>28.17475778447218</v>
       </c>
       <c r="O6" t="n">
-        <v>5.329167376091714</v>
+        <v>5.307989994759993</v>
       </c>
       <c r="P6" t="n">
-        <v>348.4164774829001</v>
+        <v>348.3912116446197</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36359,28 +36689,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001061612707339076</v>
+        <v>-0.0006716120048574782</v>
       </c>
       <c r="J7" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K7" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L7" t="n">
-        <v>1.487022542989713e-06</v>
+        <v>6.074917794363088e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>4.894123693073843</v>
+        <v>4.856936179301282</v>
       </c>
       <c r="N7" t="n">
-        <v>38.53102392937427</v>
+        <v>38.18145451453696</v>
       </c>
       <c r="O7" t="n">
-        <v>6.207336299039571</v>
+        <v>6.17911437946709</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7950772630583</v>
+        <v>346.8145661755406</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36437,28 +36767,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2272246320085411</v>
+        <v>0.2264324069879536</v>
       </c>
       <c r="J8" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07378716243252303</v>
+        <v>0.07471971157110824</v>
       </c>
       <c r="M8" t="n">
-        <v>4.605364384960405</v>
+        <v>4.570964040300876</v>
       </c>
       <c r="N8" t="n">
-        <v>32.94862806643933</v>
+        <v>32.64912354657449</v>
       </c>
       <c r="O8" t="n">
-        <v>5.740089552127155</v>
+        <v>5.713941157080153</v>
       </c>
       <c r="P8" t="n">
-        <v>346.549558327918</v>
+        <v>346.5584503659555</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36515,28 +36845,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2896343957319113</v>
+        <v>0.2903600729334221</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K9" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08618856808928455</v>
+        <v>0.08813317872927584</v>
       </c>
       <c r="M9" t="n">
-        <v>5.31757013279276</v>
+        <v>5.287281965984612</v>
       </c>
       <c r="N9" t="n">
-        <v>45.21720605225161</v>
+        <v>44.85615159144841</v>
       </c>
       <c r="O9" t="n">
-        <v>6.72437402679622</v>
+        <v>6.697473523012122</v>
       </c>
       <c r="P9" t="n">
-        <v>350.6161777738062</v>
+        <v>350.6079666171349</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36593,28 +36923,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3196829757192217</v>
+        <v>0.3183528100201601</v>
       </c>
       <c r="J10" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K10" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08965119289107393</v>
+        <v>0.09055325644940759</v>
       </c>
       <c r="M10" t="n">
-        <v>5.883906196746559</v>
+        <v>5.851180473153902</v>
       </c>
       <c r="N10" t="n">
-        <v>52.75787623651114</v>
+        <v>52.34157804062614</v>
       </c>
       <c r="O10" t="n">
-        <v>7.263461725411041</v>
+        <v>7.234747959716782</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6905132654932</v>
+        <v>356.7054170664524</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36671,28 +37001,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1317095343471669</v>
+        <v>0.1267752988702581</v>
       </c>
       <c r="J11" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K11" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01976152083634741</v>
+        <v>0.01857589742546317</v>
       </c>
       <c r="M11" t="n">
-        <v>5.283457171997163</v>
+        <v>5.285506889449723</v>
       </c>
       <c r="N11" t="n">
-        <v>43.74640228951562</v>
+        <v>43.66489687516247</v>
       </c>
       <c r="O11" t="n">
-        <v>6.614106310720717</v>
+        <v>6.607941954584836</v>
       </c>
       <c r="P11" t="n">
-        <v>359.9331467657605</v>
+        <v>359.9885312065614</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -36753,28 +37083,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4798549374958391</v>
+        <v>-0.4892474061849917</v>
       </c>
       <c r="J12" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="K12" t="n">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1446959130618385</v>
+        <v>0.1512423000688963</v>
       </c>
       <c r="M12" t="n">
-        <v>6.669194263887988</v>
+        <v>6.664239781190565</v>
       </c>
       <c r="N12" t="n">
-        <v>69.19596175631376</v>
+        <v>69.07545510561204</v>
       </c>
       <c r="O12" t="n">
-        <v>8.318411011504166</v>
+        <v>8.311164485534626</v>
       </c>
       <c r="P12" t="n">
-        <v>365.2429941200907</v>
+        <v>365.3485512186575</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -36816,7 +37146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M636"/>
+  <dimension ref="A1:M642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79422,10 +79752,412 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>-45.568398184118706,170.72784507250776</t>
+          <t>-45.568409754162424,170.7278863592513</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-45.56272009092261,170.73163311856325</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-45.563287700360384,170.7312232814861</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-45.56384966290292,170.73081109102216</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-45.564391156557,170.7303708236478</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-45.56494860965293,170.72995832147984</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-45.56551598979376,170.72957251699626</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-45.566108875869936,170.72926794793645</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-45.56669915491622,170.72896119565104</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>-45.56729430366485,170.72869466266266</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>-45.567875297672764,170.72836587342798</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>-45.56840325226646,170.72786315776503</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-45.56271941395859,170.7316317606181</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-45.56329155386493,170.73123101138697</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-45.56385495785781,170.7308229952422</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-45.564397386882256,170.73038728815177</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-45.564957342655724,170.72998246439246</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-45.56551963109057,170.72958295758528</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-45.56611064964204,170.72927341330998</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-45.56670706711396,170.72898688837284</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>-45.56730034836209,170.72871715535393</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>-45.5678783911148,170.72837790267505</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>-45.568407520178184,170.72787838745796</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-45.56272368403903,170.73164032611908</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-45.56329717789766,170.73124229286583</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-45.56385746092698,170.73082862269243</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-45.564403233144255,170.73040273772395</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-45.56496529297943,170.73000444356012</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-45.56552195191663,170.72958961202735</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-45.566112423413905,170.72927887868386</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>-45.56671418447423,170.72901000009696</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>-45.567306232291905,170.72873904984016</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>-45.56788572256749,170.72840641199613</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>-45.56842345814341,170.72793526086352</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-45.56271800795636,170.73162894027047</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-45.563294678327686,170.73123727887494</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-45.56385620939243,170.73082580896724</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-45.56440195294106,170.73039935460568</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-45.56496084409414,170.72999214433597</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-45.56551474935178,170.7295689603124</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-45.56611159313775,170.7292763204237</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>-45.56671443737526,170.72901082132586</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>-45.56730761485405,170.72874419444685</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>-45.56788652686144,170.72840953960142</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>-45.56842345814341,170.72793526086352</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-45.56272623567216,170.73164544452882</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-45.5633022811857,170.73125252976527</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-45.563861263666155,170.73083717208897</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-45.56441082901446,170.7304228108956</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-45.56496504581917,170.73000376026982</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-45.565517910477915,170.72957802411997</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-45.56611532938,170.72928783259505</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>-45.56672050699854,170.7290305308214</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>-45.56731150531841,170.7287586711323</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>-45.56790530400809,170.72848255718236</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>-45.568447531753726,170.72802116594474</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-45.56273300531001,170.7316590239856</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-45.56330899877777,170.7312660048705</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-45.56386506640473,170.7308457214867</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-45.564419150329,170.7304448011742</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-45.56497138959793,170.73002129805565</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-45.565520671460916,170.72958594061097</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-45.56611914110072,170.72929957733712</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>-45.56672820240897,170.72905551965232</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>-45.56732314454815,170.72880198155895</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>-45.56792259626568,170.7285498007651</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>-45.56846466999172,170.72808232279374</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M642"/>
+  <dimension ref="A1:M646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29287,7 +29287,7 @@
         <v>365.87</v>
       </c>
       <c r="K641" t="n">
-        <v>365.08</v>
+        <v>359.01</v>
       </c>
       <c r="L641" t="n">
         <v>352.74</v>
@@ -29332,12 +29332,192 @@
         <v>369.49</v>
       </c>
       <c r="K642" t="n">
-        <v>370.67</v>
+        <v>359.01</v>
       </c>
       <c r="L642" t="n">
         <v>357.88</v>
       </c>
       <c r="M642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="C643" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="D643" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="E643" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="F643" t="n">
+        <v>348.77</v>
+      </c>
+      <c r="G643" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="H643" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="I643" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="J643" t="n">
+        <v>369.42</v>
+      </c>
+      <c r="K643" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="L643" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>331.15</v>
+      </c>
+      <c r="C644" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="D644" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="E644" t="n">
+        <v>349.82</v>
+      </c>
+      <c r="F644" t="n">
+        <v>348.55</v>
+      </c>
+      <c r="G644" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="H644" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="I644" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="J644" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="K644" t="n">
+        <v>360.27</v>
+      </c>
+      <c r="L644" t="n">
+        <v>359</v>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="C645" t="n">
+        <v>342.79</v>
+      </c>
+      <c r="D645" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="E645" t="n">
+        <v>349.48</v>
+      </c>
+      <c r="F645" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="G645" t="n">
+        <v>345.64</v>
+      </c>
+      <c r="H645" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="I645" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="J645" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="K645" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="L645" t="n">
+        <v>358.58</v>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="C646" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="D646" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="E646" t="n">
+        <v>349.32</v>
+      </c>
+      <c r="F646" t="n">
+        <v>348.51</v>
+      </c>
+      <c r="G646" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="H646" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="I646" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="J646" t="n">
+        <v>370.63</v>
+      </c>
+      <c r="K646" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="L646" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="M646" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29354,7 +29534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B677"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36127,6 +36307,46 @@
       </c>
       <c r="B677" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -36295,28 +36515,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2544960264215813</v>
+        <v>-0.253783178019742</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K2" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08403612222297896</v>
+        <v>0.08465660057427937</v>
       </c>
       <c r="M2" t="n">
-        <v>4.777278234177593</v>
+        <v>4.751635844148614</v>
       </c>
       <c r="N2" t="n">
-        <v>36.30200331902355</v>
+        <v>36.07899755157349</v>
       </c>
       <c r="O2" t="n">
-        <v>6.025114382235706</v>
+        <v>6.006579521788877</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5920984914384</v>
+        <v>337.5840480813074</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36377,28 +36597,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2478965357620275</v>
+        <v>-0.2475302908363653</v>
       </c>
       <c r="J3" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K3" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1279827696905318</v>
+        <v>0.1291750952890071</v>
       </c>
       <c r="M3" t="n">
-        <v>3.752644471884639</v>
+        <v>3.732443010903525</v>
       </c>
       <c r="N3" t="n">
-        <v>21.53132293306938</v>
+        <v>21.40002716750137</v>
       </c>
       <c r="O3" t="n">
-        <v>4.640185657176809</v>
+        <v>4.626016338870991</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8872964823606</v>
+        <v>348.8831572650447</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36455,28 +36675,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2044100686682523</v>
+        <v>-0.2022211784151623</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08570883813508223</v>
+        <v>0.08503384250106061</v>
       </c>
       <c r="M4" t="n">
-        <v>3.749318894847312</v>
+        <v>3.736292974167972</v>
       </c>
       <c r="N4" t="n">
-        <v>22.92026947862799</v>
+        <v>22.79670452544322</v>
       </c>
       <c r="O4" t="n">
-        <v>4.787511825429572</v>
+        <v>4.774589461455636</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0280120117633</v>
+        <v>353.0032945307493</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36533,28 +36753,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1720802519957282</v>
+        <v>-0.1683804829440036</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06712179491509185</v>
+        <v>0.06512727071507696</v>
       </c>
       <c r="M5" t="n">
-        <v>3.640905132957771</v>
+        <v>3.634728388116875</v>
       </c>
       <c r="N5" t="n">
-        <v>21.16311975027817</v>
+        <v>21.08524659560005</v>
       </c>
       <c r="O5" t="n">
-        <v>4.600339090793001</v>
+        <v>4.591867440987387</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5518308040016</v>
+        <v>351.5100521942627</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36611,28 +36831,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0707287620200174</v>
+        <v>-0.06807377177054784</v>
       </c>
       <c r="J6" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009047756101805415</v>
+        <v>0.00849357845406673</v>
       </c>
       <c r="M6" t="n">
-        <v>4.066754717422142</v>
+        <v>4.054522056528643</v>
       </c>
       <c r="N6" t="n">
-        <v>28.17475778447218</v>
+        <v>28.02657496342492</v>
       </c>
       <c r="O6" t="n">
-        <v>5.307989994759993</v>
+        <v>5.294013124598854</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3912116446197</v>
+        <v>348.3612292289797</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36689,28 +36909,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0006716120048574782</v>
+        <v>-0.001896568853871393</v>
       </c>
       <c r="J7" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L7" t="n">
-        <v>6.074917794363088e-07</v>
+        <v>4.91044062245205e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.856936179301282</v>
+        <v>4.832868886421623</v>
       </c>
       <c r="N7" t="n">
-        <v>38.18145451453696</v>
+        <v>37.95073592074561</v>
       </c>
       <c r="O7" t="n">
-        <v>6.17911437946709</v>
+        <v>6.160416862578831</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8145661755406</v>
+        <v>346.8283997560552</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36767,28 +36987,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2264324069879536</v>
+        <v>0.2266809933166963</v>
       </c>
       <c r="J8" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K8" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07471971157110824</v>
+        <v>0.07582558007548867</v>
       </c>
       <c r="M8" t="n">
-        <v>4.570964040300876</v>
+        <v>4.543662289249866</v>
       </c>
       <c r="N8" t="n">
-        <v>32.64912354657449</v>
+        <v>32.44695798345766</v>
       </c>
       <c r="O8" t="n">
-        <v>5.713941157080153</v>
+        <v>5.696223133222369</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5584503659555</v>
+        <v>346.5556424428233</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36845,28 +37065,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2903600729334221</v>
+        <v>0.2981153121021834</v>
       </c>
       <c r="J9" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K9" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08813317872927584</v>
+        <v>0.09317868225323189</v>
       </c>
       <c r="M9" t="n">
-        <v>5.287281965984612</v>
+        <v>5.288434447326797</v>
       </c>
       <c r="N9" t="n">
-        <v>44.85615159144841</v>
+        <v>44.81044878226</v>
       </c>
       <c r="O9" t="n">
-        <v>6.697473523012122</v>
+        <v>6.694060709484192</v>
       </c>
       <c r="P9" t="n">
-        <v>350.6079666171349</v>
+        <v>350.5203796007339</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36923,28 +37143,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3183528100201601</v>
+        <v>0.3244237899826748</v>
       </c>
       <c r="J10" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K10" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09055325644940759</v>
+        <v>0.09465227032944534</v>
       </c>
       <c r="M10" t="n">
-        <v>5.851180473153902</v>
+        <v>5.841535764062873</v>
       </c>
       <c r="N10" t="n">
-        <v>52.34157804062614</v>
+        <v>52.15732848249893</v>
       </c>
       <c r="O10" t="n">
-        <v>7.234747959716782</v>
+        <v>7.22200307965172</v>
       </c>
       <c r="P10" t="n">
-        <v>356.7054170664524</v>
+        <v>356.6368535413654</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37001,28 +37221,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1267752988702581</v>
+        <v>0.1165451606453879</v>
       </c>
       <c r="J11" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K11" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01857589742546317</v>
+        <v>0.01594013820355766</v>
       </c>
       <c r="M11" t="n">
-        <v>5.285506889449723</v>
+        <v>5.273518147470055</v>
       </c>
       <c r="N11" t="n">
-        <v>43.66489687516247</v>
+        <v>43.44336882254548</v>
       </c>
       <c r="O11" t="n">
-        <v>6.607941954584836</v>
+        <v>6.591158382450347</v>
       </c>
       <c r="P11" t="n">
-        <v>359.9885312065614</v>
+        <v>360.1038613633883</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37083,28 +37303,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4892474061849917</v>
+        <v>-0.4815722832519614</v>
       </c>
       <c r="J12" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K12" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1512423000688963</v>
+        <v>0.1485453970296574</v>
       </c>
       <c r="M12" t="n">
-        <v>6.664239781190565</v>
+        <v>6.66463429513854</v>
       </c>
       <c r="N12" t="n">
-        <v>69.07545510561204</v>
+        <v>68.87011932174694</v>
       </c>
       <c r="O12" t="n">
-        <v>8.311164485534626</v>
+        <v>8.298802282362615</v>
       </c>
       <c r="P12" t="n">
-        <v>365.3485512186575</v>
+        <v>365.2618764430216</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37146,7 +37366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M642"/>
+  <dimension ref="A1:M646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80082,7 +80302,7 @@
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>-45.56790530400809,170.72848255718236</t>
+          <t>-45.56788652686144,170.72840953960142</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -80149,7 +80369,7 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>-45.56792259626568,170.7285498007651</t>
+          <t>-45.56788652686144,170.72840953960142</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -80158,6 +80378,274 @@
         </is>
       </c>
       <c r="M642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-45.562728422786094,170.7316498317376</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-45.56330399963963,170.7312559768849</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-45.563859482636495,170.73083316794109</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-45.564411725156226,170.7304251790791</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-45.56496611684694,170.73000672119443</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-45.56551695013588,170.72957527055806</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-45.566114763282755,170.72928608832657</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>-45.566730623029926,170.7290633799903</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>-45.567322919480326,170.72880114406433</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>-45.567885289486085,170.728404727901</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>-45.56846443659182,170.7280814899181</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-45.56272696471015,170.73164690693173</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-45.56330264570622,170.73125326097247</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-45.56385731651915,170.7308282980318</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-45.5644076711812,170.7304144658685</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-45.56496521059268,170.73000421579667</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-45.56551963109057,170.72958295758528</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-45.566115216160554,170.72928748374136</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>-45.566731417860574,170.72906596099693</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>-45.56732301593796,170.7288015029906</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>-45.56789042459253,170.72842469645923</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>-45.568468404389534,170.72809564880484</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-45.562729255972314,170.73165150305528</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-45.56330722824977,170.73126245329206</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-45.563855920576756,170.73082515964606</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-45.56440622028463,170.7304106316672</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-45.5649650046258,170.7300036463881</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-45.5655173502784,170.7295764178755</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-45.56611540485962,170.72928806516418</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>-45.56673788488962,170.72908696100828</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>-45.56732645625974,170.72881430469477</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>-45.56789030085506,170.72842421528912</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>-45.56846700399054,170.72809065155047</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-45.56272706885843,170.7316471158464</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-45.56330967574433,170.731267362827</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-45.563855776168914,170.73082483498547</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-45.56440553750973,170.73040882733724</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-45.56496504581917,170.73000376026982</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-45.5655185507059,170.72957985982796</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-45.56611597095683,170.7292898094327</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>-45.56673907713478,170.7290908325193</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>-45.5673268099376,170.72881562075787</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>-45.56788921815215,170.72842000505065</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>-45.56846403647767,170.72808006213134</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
